--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942932</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129941278</v>
       </c>
       <c r="B3" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129941035</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942932</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129941278</v>
       </c>
       <c r="B3" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129941035</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942932</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129941278</v>
       </c>
       <c r="B3" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129941035</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129941278</v>
       </c>
       <c r="B3" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129942932</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129941278</v>
       </c>
       <c r="B3" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129941035</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129942932</v>
+        <v>129941278</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511998</v>
+        <v>512017</v>
       </c>
       <c r="R2" t="n">
-        <v>6628751</v>
+        <v>6628735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129941278</v>
+        <v>129941035</v>
       </c>
       <c r="B3" t="n">
-        <v>93048</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129941035</v>
+        <v>129942032</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Daniels mossen, Daniels mossen, Vstm</t>
+          <t>Källrännilsberget, Källrännilsberget, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512017</v>
+        <v>512123</v>
       </c>
       <c r="R4" t="n">
-        <v>6628735</v>
+        <v>6628911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +993,444 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129942932</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Daniels mossen, Daniels mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>511998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6628751</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129940502</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Daniels mossen, Daniels mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512096</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6628694</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129941407</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källrännilsberget, Källrännilsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512123</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6628911</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129941490</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källrännilsberget, Källrännilsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512123</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628911</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51851-2025 artfynd.xlsx
+++ b/artfynd/A 51851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129941278</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129941035</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129942032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129942932</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129940502</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129941407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,8 +1466,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129941490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>